--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.21310571669603</v>
+        <v>7.672129678963106</v>
       </c>
       <c r="D2" t="n">
-        <v>47.19035156956769</v>
+        <v>7.668432130054749</v>
       </c>
       <c r="E2" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F2" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.91031884231797</v>
+        <v>5.510426811876671</v>
       </c>
       <c r="D3" t="n">
-        <v>33.88597778397466</v>
+        <v>5.506471389895882</v>
       </c>
       <c r="E3" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F3" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.89403644695377</v>
+        <v>10.22028092262999</v>
       </c>
       <c r="D4" t="n">
-        <v>62.79070566348765</v>
+        <v>10.20348967031674</v>
       </c>
       <c r="E4" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F4" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.99253099798548</v>
+        <v>5.36128628717264</v>
       </c>
       <c r="D5" t="n">
-        <v>32.78337080858334</v>
+        <v>5.327297756394792</v>
       </c>
       <c r="E5" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F5" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.83799374750308</v>
+        <v>9.07367398396925</v>
       </c>
       <c r="D6" t="n">
-        <v>55.66449733671779</v>
+        <v>9.045480817216642</v>
       </c>
       <c r="E6" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F6" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>70.65670818930934</v>
+        <v>11.48171508076277</v>
       </c>
       <c r="D7" t="n">
-        <v>70.48567222727041</v>
+        <v>11.45392173693144</v>
       </c>
       <c r="E7" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F7" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.76072927308593</v>
+        <v>5.648618506876463</v>
       </c>
       <c r="D8" t="n">
-        <v>34.45674707529806</v>
+        <v>5.599221399735935</v>
       </c>
       <c r="E8" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F8" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>66.45857043761245</v>
+        <v>10.79951769611202</v>
       </c>
       <c r="D9" t="n">
-        <v>66.24315382126626</v>
+        <v>10.76451249595577</v>
       </c>
       <c r="E9" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F9" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.35299576496648</v>
+        <v>6.232361811807053</v>
       </c>
       <c r="D10" t="n">
-        <v>38.13479239276857</v>
+        <v>6.196903763824894</v>
       </c>
       <c r="E10" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F10" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73067309168604</v>
+        <v>6.293734377398981</v>
       </c>
       <c r="D11" t="n">
-        <v>38.6861886818336</v>
+        <v>6.28650566079796</v>
       </c>
       <c r="E11" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F11" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>51.4297600375478</v>
+        <v>8.357336006101518</v>
       </c>
       <c r="D12" t="n">
-        <v>51.12514077810405</v>
+        <v>8.30783537644191</v>
       </c>
       <c r="E12" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F12" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>64.72590835118449</v>
+        <v>10.51796010706748</v>
       </c>
       <c r="D13" t="n">
-        <v>64.42708597278181</v>
+        <v>10.46940147057705</v>
       </c>
       <c r="E13" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F13" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.39578011602885</v>
+        <v>4.451814268854688</v>
       </c>
       <c r="D14" t="n">
-        <v>27.46961951817613</v>
+        <v>4.463813171703621</v>
       </c>
       <c r="E14" t="n">
-        <v>14.22848878776996</v>
+        <v>2.312129428012619</v>
       </c>
       <c r="F14" t="n">
-        <v>14.18531927522361</v>
+        <v>2.305114382223837</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
